--- a/output/yearly_total_coral_cover_iteration_11_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_11_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.29009152347773</v>
+        <v>1.264791885139289</v>
       </c>
       <c r="C3" t="n">
-        <v>4.617500010586284</v>
+        <v>4.689776276572934</v>
       </c>
       <c r="D3" t="n">
-        <v>6.076502965677666</v>
+        <v>6.097532001502633</v>
       </c>
       <c r="E3" t="n">
-        <v>11.98409449974168</v>
+        <v>12.05210016321486</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.470363944832919</v>
+        <v>1.402169911469459</v>
       </c>
       <c r="C4" t="n">
-        <v>5.094114837203872</v>
+        <v>5.280792049086707</v>
       </c>
       <c r="D4" t="n">
-        <v>6.290553660470751</v>
+        <v>6.345530160696392</v>
       </c>
       <c r="E4" t="n">
-        <v>12.85503244250754</v>
+        <v>13.02849212125256</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.705081250039358</v>
+        <v>1.585045779530682</v>
       </c>
       <c r="C5" t="n">
-        <v>5.676264172328819</v>
+        <v>6.101191169448607</v>
       </c>
       <c r="D5" t="n">
-        <v>6.556947514585729</v>
+        <v>6.675974683494994</v>
       </c>
       <c r="E5" t="n">
-        <v>13.93829293695391</v>
+        <v>14.36221163247428</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.975667147281063</v>
+        <v>1.782974270512964</v>
       </c>
       <c r="C6" t="n">
-        <v>6.350606821995359</v>
+        <v>7.098113794054913</v>
       </c>
       <c r="D6" t="n">
-        <v>6.83897271943193</v>
+        <v>7.087249606273089</v>
       </c>
       <c r="E6" t="n">
-        <v>15.16524668870835</v>
+        <v>15.96833767084097</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.2979809757213</v>
+        <v>2.001739243226227</v>
       </c>
       <c r="C7" t="n">
-        <v>7.115725384641571</v>
+        <v>8.312320576363229</v>
       </c>
       <c r="D7" t="n">
-        <v>7.154169131640695</v>
+        <v>7.484257035772531</v>
       </c>
       <c r="E7" t="n">
-        <v>16.56787549200357</v>
+        <v>17.79831685536199</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.533014775098249</v>
+        <v>1.214022074646052</v>
       </c>
       <c r="C8" t="n">
-        <v>4.68660853836104</v>
+        <v>6.027273724278675</v>
       </c>
       <c r="D8" t="n">
-        <v>5.313014392076444</v>
+        <v>5.757544535767461</v>
       </c>
       <c r="E8" t="n">
-        <v>11.53263770553573</v>
+        <v>12.99884033469219</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.002161346052071</v>
+        <v>1.506228425713703</v>
       </c>
       <c r="C9" t="n">
-        <v>5.611061592647634</v>
+        <v>7.549528062578145</v>
       </c>
       <c r="D9" t="n">
-        <v>5.698205243971641</v>
+        <v>6.231406712958687</v>
       </c>
       <c r="E9" t="n">
-        <v>13.31142818267135</v>
+        <v>15.28716320125054</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.502014337435085</v>
+        <v>1.80392044123154</v>
       </c>
       <c r="C10" t="n">
-        <v>6.648316994272077</v>
+        <v>9.207309133981198</v>
       </c>
       <c r="D10" t="n">
-        <v>6.149187423757901</v>
+        <v>6.697227327666188</v>
       </c>
       <c r="E10" t="n">
-        <v>15.29951875546506</v>
+        <v>17.70845690287893</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.021137628167165</v>
+        <v>2.091587804772262</v>
       </c>
       <c r="C11" t="n">
-        <v>7.745288215298392</v>
+        <v>10.98235662740981</v>
       </c>
       <c r="D11" t="n">
-        <v>6.556394607811161</v>
+        <v>7.146577281507961</v>
       </c>
       <c r="E11" t="n">
-        <v>17.32282045127672</v>
+        <v>20.22052171369004</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.566989969742286</v>
+        <v>2.373683066968118</v>
       </c>
       <c r="C12" t="n">
-        <v>8.888526711276221</v>
+        <v>12.7837556897911</v>
       </c>
       <c r="D12" t="n">
-        <v>6.985945039342216</v>
+        <v>7.630354658042263</v>
       </c>
       <c r="E12" t="n">
-        <v>19.44146172036072</v>
+        <v>22.78779341480148</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.12045945802677</v>
+        <v>2.623844717506761</v>
       </c>
       <c r="C13" t="n">
-        <v>10.05227923924559</v>
+        <v>14.63388201402866</v>
       </c>
       <c r="D13" t="n">
-        <v>7.44031253606116</v>
+        <v>8.020604201459784</v>
       </c>
       <c r="E13" t="n">
-        <v>21.61305123333352</v>
+        <v>25.27833093299521</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.36763185094682</v>
+        <v>1.503890220750477</v>
       </c>
       <c r="C14" t="n">
-        <v>7.137266539966141</v>
+        <v>10.16614473963136</v>
       </c>
       <c r="D14" t="n">
-        <v>5.681982648052925</v>
+        <v>6.069007228021103</v>
       </c>
       <c r="E14" t="n">
-        <v>15.18688103896589</v>
+        <v>17.73904218840294</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.508728631001172</v>
+        <v>1.512372520915169</v>
       </c>
       <c r="C15" t="n">
-        <v>7.448833991385909</v>
+        <v>11.03597320559403</v>
       </c>
       <c r="D15" t="n">
-        <v>5.660099491725264</v>
+        <v>6.051640111132977</v>
       </c>
       <c r="E15" t="n">
-        <v>15.61766211411235</v>
+        <v>18.59998583764218</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3.003833815729881</v>
+        <v>1.72526451058109</v>
       </c>
       <c r="C16" t="n">
-        <v>8.674595087523263</v>
+        <v>13.02598561957936</v>
       </c>
       <c r="D16" t="n">
-        <v>6.072001558519055</v>
+        <v>6.446155426084557</v>
       </c>
       <c r="E16" t="n">
-        <v>17.7504304617722</v>
+        <v>21.19740555624501</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.475712455707352</v>
+        <v>1.36651426449522</v>
       </c>
       <c r="C17" t="n">
-        <v>7.91812902896997</v>
+        <v>11.93112094484923</v>
       </c>
       <c r="D17" t="n">
-        <v>5.621222282637089</v>
+        <v>5.929530331678758</v>
       </c>
       <c r="E17" t="n">
-        <v>16.01506376731441</v>
+        <v>19.22716554102321</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.913856638635661</v>
+        <v>1.535001805498058</v>
       </c>
       <c r="C18" t="n">
-        <v>9.19415560756476</v>
+        <v>13.91236635183564</v>
       </c>
       <c r="D18" t="n">
-        <v>6.041380847623598</v>
+        <v>6.329867410516522</v>
       </c>
       <c r="E18" t="n">
-        <v>18.14939309382402</v>
+        <v>21.77723556785022</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>3.009203975672111</v>
+        <v>1.51830227704882</v>
       </c>
       <c r="C19" t="n">
-        <v>9.800129560534062</v>
+        <v>14.8373494038229</v>
       </c>
       <c r="D19" t="n">
-        <v>6.148842951330453</v>
+        <v>6.390843760427291</v>
       </c>
       <c r="E19" t="n">
-        <v>18.95817648753663</v>
+        <v>22.74649544129901</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>3.444805432046421</v>
+        <v>1.663934731496792</v>
       </c>
       <c r="C20" t="n">
-        <v>11.29830600964582</v>
+        <v>16.96726086566339</v>
       </c>
       <c r="D20" t="n">
-        <v>6.636388678736462</v>
+        <v>6.789531503121921</v>
       </c>
       <c r="E20" t="n">
-        <v>21.37950012042871</v>
+        <v>25.4207271002821</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>2.097327255536546</v>
+        <v>0.9756608684804804</v>
       </c>
       <c r="C21" t="n">
-        <v>8.406960845868543</v>
+        <v>12.37043340754559</v>
       </c>
       <c r="D21" t="n">
-        <v>5.546491647389822</v>
+        <v>5.646276484049469</v>
       </c>
       <c r="E21" t="n">
-        <v>16.05077974879491</v>
+        <v>18.99237076007554</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_11_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_11_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.264791885139289</v>
+        <v>1.288275290224873</v>
       </c>
       <c r="C3" t="n">
-        <v>4.689776276572934</v>
+        <v>4.662974564246996</v>
       </c>
       <c r="D3" t="n">
-        <v>6.097532001502633</v>
+        <v>6.089255868355833</v>
       </c>
       <c r="E3" t="n">
-        <v>12.05210016321486</v>
+        <v>12.0405057228277</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.402169911469459</v>
+        <v>1.471610911335311</v>
       </c>
       <c r="C4" t="n">
-        <v>5.280792049086707</v>
+        <v>5.22741499965084</v>
       </c>
       <c r="D4" t="n">
-        <v>6.345530160696392</v>
+        <v>6.300124562874329</v>
       </c>
       <c r="E4" t="n">
-        <v>13.02849212125256</v>
+        <v>12.99915047386048</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.585045779530682</v>
+        <v>1.720259898378029</v>
       </c>
       <c r="C5" t="n">
-        <v>6.101191169448607</v>
+        <v>5.939668605126948</v>
       </c>
       <c r="D5" t="n">
-        <v>6.675974683494994</v>
+        <v>6.638159409299718</v>
       </c>
       <c r="E5" t="n">
-        <v>14.36221163247428</v>
+        <v>14.2980879128047</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1.782974270512964</v>
+        <v>2.002779035056841</v>
       </c>
       <c r="C6" t="n">
-        <v>7.098113794054913</v>
+        <v>6.772036010929101</v>
       </c>
       <c r="D6" t="n">
-        <v>7.087249606273089</v>
+        <v>6.992221655000534</v>
       </c>
       <c r="E6" t="n">
-        <v>15.96833767084097</v>
+        <v>15.76703670098648</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.001739243226227</v>
+        <v>2.326220184458816</v>
       </c>
       <c r="C7" t="n">
-        <v>8.312320576363229</v>
+        <v>7.695768032959574</v>
       </c>
       <c r="D7" t="n">
-        <v>7.484257035772531</v>
+        <v>7.42786661680792</v>
       </c>
       <c r="E7" t="n">
-        <v>17.79831685536199</v>
+        <v>17.44985483422631</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.214022074646052</v>
+        <v>1.519886264338656</v>
       </c>
       <c r="C8" t="n">
-        <v>6.027273724278675</v>
+        <v>5.187060033464984</v>
       </c>
       <c r="D8" t="n">
-        <v>5.757544535767461</v>
+        <v>5.731529881561119</v>
       </c>
       <c r="E8" t="n">
-        <v>12.99884033469219</v>
+        <v>12.43847617936476</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.506228425713703</v>
+        <v>1.958305957905666</v>
       </c>
       <c r="C9" t="n">
-        <v>7.549528062578145</v>
+        <v>6.192853195162704</v>
       </c>
       <c r="D9" t="n">
-        <v>6.231406712958687</v>
+        <v>6.321665450153913</v>
       </c>
       <c r="E9" t="n">
-        <v>15.28716320125054</v>
+        <v>14.47282460322228</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.80392044123154</v>
+        <v>2.420933033617797</v>
       </c>
       <c r="C10" t="n">
-        <v>9.207309133981198</v>
+        <v>7.26107873082807</v>
       </c>
       <c r="D10" t="n">
-        <v>6.697227327666188</v>
+        <v>6.937679069024256</v>
       </c>
       <c r="E10" t="n">
-        <v>17.70845690287893</v>
+        <v>16.61969083347012</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.091587804772262</v>
+        <v>2.889783102715394</v>
       </c>
       <c r="C11" t="n">
-        <v>10.98235662740981</v>
+        <v>8.371431773660637</v>
       </c>
       <c r="D11" t="n">
-        <v>7.146577281507961</v>
+        <v>7.501081521993788</v>
       </c>
       <c r="E11" t="n">
-        <v>20.22052171369004</v>
+        <v>18.76229639836982</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.373683066968118</v>
+        <v>3.371719762562152</v>
       </c>
       <c r="C12" t="n">
-        <v>12.7837556897911</v>
+        <v>9.507325943960454</v>
       </c>
       <c r="D12" t="n">
-        <v>7.630354658042263</v>
+        <v>8.076411294648029</v>
       </c>
       <c r="E12" t="n">
-        <v>22.78779341480148</v>
+        <v>20.95545700117064</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.623844717506761</v>
+        <v>3.857482038661618</v>
       </c>
       <c r="C13" t="n">
-        <v>14.63388201402866</v>
+        <v>10.64335566251154</v>
       </c>
       <c r="D13" t="n">
-        <v>8.020604201459784</v>
+        <v>8.700448112233419</v>
       </c>
       <c r="E13" t="n">
-        <v>25.27833093299521</v>
+        <v>23.20128581340657</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.503890220750477</v>
+        <v>2.214381034313893</v>
       </c>
       <c r="C14" t="n">
-        <v>10.16614473963136</v>
+        <v>7.591531020198183</v>
       </c>
       <c r="D14" t="n">
-        <v>6.069007228021103</v>
+        <v>6.635092771766856</v>
       </c>
       <c r="E14" t="n">
-        <v>17.73904218840294</v>
+        <v>16.44100482627893</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.512372520915169</v>
+        <v>2.319192419219283</v>
       </c>
       <c r="C15" t="n">
-        <v>11.03597320559403</v>
+        <v>7.833512194340938</v>
       </c>
       <c r="D15" t="n">
-        <v>6.051640111132977</v>
+        <v>6.737165080577397</v>
       </c>
       <c r="E15" t="n">
-        <v>18.59998583764218</v>
+        <v>16.88986969413762</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.72526451058109</v>
+        <v>2.742659473969102</v>
       </c>
       <c r="C16" t="n">
-        <v>13.02598561957936</v>
+        <v>8.992406454342042</v>
       </c>
       <c r="D16" t="n">
-        <v>6.446155426084557</v>
+        <v>7.309121475594544</v>
       </c>
       <c r="E16" t="n">
-        <v>21.19740555624501</v>
+        <v>19.04418740390569</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.36651426449522</v>
+        <v>2.241909239940974</v>
       </c>
       <c r="C17" t="n">
-        <v>11.93112094484923</v>
+        <v>8.034259964905326</v>
       </c>
       <c r="D17" t="n">
-        <v>5.929530331678758</v>
+        <v>6.877613907146944</v>
       </c>
       <c r="E17" t="n">
-        <v>19.22716554102321</v>
+        <v>17.15378311199325</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.535001805498058</v>
+        <v>2.611988854533851</v>
       </c>
       <c r="C18" t="n">
-        <v>13.91236635183564</v>
+        <v>9.203197503920874</v>
       </c>
       <c r="D18" t="n">
-        <v>6.329867410516522</v>
+        <v>7.391352663302259</v>
       </c>
       <c r="E18" t="n">
-        <v>21.77723556785022</v>
+        <v>19.20653902175698</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.51830227704882</v>
+        <v>2.677913212874024</v>
       </c>
       <c r="C19" t="n">
-        <v>14.8373494038229</v>
+        <v>9.700472351075968</v>
       </c>
       <c r="D19" t="n">
-        <v>6.390843760427291</v>
+        <v>7.556669159220379</v>
       </c>
       <c r="E19" t="n">
-        <v>22.74649544129901</v>
+        <v>19.93505472317037</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.663934731496792</v>
+        <v>3.052145620255867</v>
       </c>
       <c r="C20" t="n">
-        <v>16.96726086566339</v>
+        <v>11.08646449002345</v>
       </c>
       <c r="D20" t="n">
-        <v>6.789531503121921</v>
+        <v>8.071684187391213</v>
       </c>
       <c r="E20" t="n">
-        <v>25.4207271002821</v>
+        <v>22.21029429767053</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.9756608684804804</v>
+        <v>1.84976975443367</v>
       </c>
       <c r="C21" t="n">
-        <v>12.37043340754559</v>
+        <v>8.233142414831644</v>
       </c>
       <c r="D21" t="n">
-        <v>5.646276484049469</v>
+        <v>6.78073504369187</v>
       </c>
       <c r="E21" t="n">
-        <v>18.99237076007554</v>
+        <v>16.86364721295718</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_total_coral_cover_iteration_11_growth_param_0.5.xlsx
+++ b/output/yearly_total_coral_cover_iteration_11_growth_param_0.5.xlsx
@@ -477,16 +477,16 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1.288275290224873</v>
+        <v>2.590488101694376</v>
       </c>
       <c r="C3" t="n">
-        <v>4.662974564246996</v>
+        <v>7.655636314642004</v>
       </c>
       <c r="D3" t="n">
-        <v>6.089255868355833</v>
+        <v>8.206250150269746</v>
       </c>
       <c r="E3" t="n">
-        <v>12.0405057228277</v>
+        <v>18.45237456660612</v>
       </c>
     </row>
     <row r="4">
@@ -494,16 +494,16 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.471610911335311</v>
+        <v>1.070964224121427</v>
       </c>
       <c r="C4" t="n">
-        <v>5.22741499965084</v>
+        <v>4.384697989977234</v>
       </c>
       <c r="D4" t="n">
-        <v>6.300124562874329</v>
+        <v>5.779990861767197</v>
       </c>
       <c r="E4" t="n">
-        <v>12.99915047386048</v>
+        <v>11.23565307586586</v>
       </c>
     </row>
     <row r="5">
@@ -511,16 +511,16 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1.720259898378029</v>
+        <v>1.168425875993372</v>
       </c>
       <c r="C5" t="n">
-        <v>5.939668605126948</v>
+        <v>4.932984908175599</v>
       </c>
       <c r="D5" t="n">
-        <v>6.638159409299718</v>
+        <v>6.028633006643163</v>
       </c>
       <c r="E5" t="n">
-        <v>14.2980879128047</v>
+        <v>12.13004379081213</v>
       </c>
     </row>
     <row r="6">
@@ -528,16 +528,16 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>2.002779035056841</v>
+        <v>1.286355937886063</v>
       </c>
       <c r="C6" t="n">
-        <v>6.772036010929101</v>
+        <v>5.645063932454693</v>
       </c>
       <c r="D6" t="n">
-        <v>6.992221655000534</v>
+        <v>6.30082263359348</v>
       </c>
       <c r="E6" t="n">
-        <v>15.76703670098648</v>
+        <v>13.23224250393424</v>
       </c>
     </row>
     <row r="7">
@@ -545,16 +545,16 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2.326220184458816</v>
+        <v>1.41619072223596</v>
       </c>
       <c r="C7" t="n">
-        <v>7.695768032959574</v>
+        <v>6.516903416892814</v>
       </c>
       <c r="D7" t="n">
-        <v>7.42786661680792</v>
+        <v>6.643282619490357</v>
       </c>
       <c r="E7" t="n">
-        <v>17.44985483422631</v>
+        <v>14.57637675861913</v>
       </c>
     </row>
     <row r="8">
@@ -562,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.519886264338656</v>
+        <v>1.557167481584129</v>
       </c>
       <c r="C8" t="n">
-        <v>5.187060033464984</v>
+        <v>7.546620662754908</v>
       </c>
       <c r="D8" t="n">
-        <v>5.731529881561119</v>
+        <v>7.013632050432125</v>
       </c>
       <c r="E8" t="n">
-        <v>12.43847617936476</v>
+        <v>16.11742019477116</v>
       </c>
     </row>
     <row r="9">
@@ -579,16 +579,16 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.958305957905666</v>
+        <v>1.707513581985556</v>
       </c>
       <c r="C9" t="n">
-        <v>6.192853195162704</v>
+        <v>8.715787941543391</v>
       </c>
       <c r="D9" t="n">
-        <v>6.321665450153913</v>
+        <v>7.340246819565688</v>
       </c>
       <c r="E9" t="n">
-        <v>14.47282460322228</v>
+        <v>17.76354834309464</v>
       </c>
     </row>
     <row r="10">
@@ -596,16 +596,16 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.420933033617797</v>
+        <v>1.069771203409579</v>
       </c>
       <c r="C10" t="n">
-        <v>7.26107873082807</v>
+        <v>6.507799364434215</v>
       </c>
       <c r="D10" t="n">
-        <v>6.937679069024256</v>
+        <v>5.768592430521578</v>
       </c>
       <c r="E10" t="n">
-        <v>16.61969083347012</v>
+        <v>13.34616299836537</v>
       </c>
     </row>
     <row r="11">
@@ -613,16 +613,16 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.889783102715394</v>
+        <v>1.02430646722591</v>
       </c>
       <c r="C11" t="n">
-        <v>8.371431773660637</v>
+        <v>6.905907875983338</v>
       </c>
       <c r="D11" t="n">
-        <v>7.501081521993788</v>
+        <v>5.589217307478643</v>
       </c>
       <c r="E11" t="n">
-        <v>18.76229639836982</v>
+        <v>13.51943165068789</v>
       </c>
     </row>
     <row r="12">
@@ -630,16 +630,16 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.371719762562152</v>
+        <v>1.1341345829</v>
       </c>
       <c r="C12" t="n">
-        <v>9.507325943960454</v>
+        <v>8.189120847773216</v>
       </c>
       <c r="D12" t="n">
-        <v>8.076411294648029</v>
+        <v>5.967592690172407</v>
       </c>
       <c r="E12" t="n">
-        <v>20.95545700117064</v>
+        <v>15.29084812084562</v>
       </c>
     </row>
     <row r="13">
@@ -647,16 +647,16 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>3.857482038661618</v>
+        <v>0.9189747560372693</v>
       </c>
       <c r="C13" t="n">
-        <v>10.64335566251154</v>
+        <v>7.836634152040442</v>
       </c>
       <c r="D13" t="n">
-        <v>8.700448112233419</v>
+        <v>5.416468981439375</v>
       </c>
       <c r="E13" t="n">
-        <v>23.20128581340657</v>
+        <v>14.17207788951709</v>
       </c>
     </row>
     <row r="14">
@@ -664,16 +664,16 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>2.214381034313893</v>
+        <v>1.022117169845439</v>
       </c>
       <c r="C14" t="n">
-        <v>7.591531020198183</v>
+        <v>9.209176347439737</v>
       </c>
       <c r="D14" t="n">
-        <v>6.635092771766856</v>
+        <v>5.735625342612971</v>
       </c>
       <c r="E14" t="n">
-        <v>16.44100482627893</v>
+        <v>15.96691885989815</v>
       </c>
     </row>
     <row r="15">
@@ -681,16 +681,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2.319192419219283</v>
+        <v>1.013595599772577</v>
       </c>
       <c r="C15" t="n">
-        <v>7.833512194340938</v>
+        <v>9.975872217071284</v>
       </c>
       <c r="D15" t="n">
-        <v>6.737165080577397</v>
+        <v>5.755221026789736</v>
       </c>
       <c r="E15" t="n">
-        <v>16.88986969413762</v>
+        <v>16.7446888436336</v>
       </c>
     </row>
     <row r="16">
@@ -698,16 +698,16 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.742659473969102</v>
+        <v>1.131258062126557</v>
       </c>
       <c r="C16" t="n">
-        <v>8.992406454342042</v>
+        <v>11.7533657055183</v>
       </c>
       <c r="D16" t="n">
-        <v>7.309121475594544</v>
+        <v>6.199353870713951</v>
       </c>
       <c r="E16" t="n">
-        <v>19.04418740390569</v>
+        <v>19.08397763835881</v>
       </c>
     </row>
     <row r="17">
@@ -715,16 +715,16 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.241909239940974</v>
+        <v>0.6896777622333843</v>
       </c>
       <c r="C17" t="n">
-        <v>8.034259964905326</v>
+        <v>8.910548330761943</v>
       </c>
       <c r="D17" t="n">
-        <v>6.877613907146944</v>
+        <v>5.148716930060142</v>
       </c>
       <c r="E17" t="n">
-        <v>17.15378311199325</v>
+        <v>14.74894302305547</v>
       </c>
     </row>
     <row r="18">
@@ -732,16 +732,16 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.611988854533851</v>
+        <v>0.5639453337504953</v>
       </c>
       <c r="C18" t="n">
-        <v>9.203197503920874</v>
+        <v>8.029203964228454</v>
       </c>
       <c r="D18" t="n">
-        <v>7.391352663302259</v>
+        <v>4.662977618429948</v>
       </c>
       <c r="E18" t="n">
-        <v>19.20653902175698</v>
+        <v>13.2561269164089</v>
       </c>
     </row>
     <row r="19">
@@ -749,16 +749,16 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2.677913212874024</v>
+        <v>0.6737341795164161</v>
       </c>
       <c r="C19" t="n">
-        <v>9.700472351075968</v>
+        <v>10.05525633643668</v>
       </c>
       <c r="D19" t="n">
-        <v>7.556669159220379</v>
+        <v>5.112971496148516</v>
       </c>
       <c r="E19" t="n">
-        <v>19.93505472317037</v>
+        <v>15.84196201210161</v>
       </c>
     </row>
     <row r="20">
@@ -766,16 +766,16 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>3.052145620255867</v>
+        <v>0.7759537504825941</v>
       </c>
       <c r="C20" t="n">
-        <v>11.08646449002345</v>
+        <v>12.2012390081957</v>
       </c>
       <c r="D20" t="n">
-        <v>8.071684187391213</v>
+        <v>5.614438406000744</v>
       </c>
       <c r="E20" t="n">
-        <v>22.21029429767053</v>
+        <v>18.59163116467904</v>
       </c>
     </row>
     <row r="21">
@@ -783,16 +783,16 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>1.84976975443367</v>
+        <v>0.8694946717432301</v>
       </c>
       <c r="C21" t="n">
-        <v>8.233142414831644</v>
+        <v>14.45985759406295</v>
       </c>
       <c r="D21" t="n">
-        <v>6.78073504369187</v>
+        <v>6.037640388870416</v>
       </c>
       <c r="E21" t="n">
-        <v>16.86364721295718</v>
+        <v>21.3669926546766</v>
       </c>
     </row>
   </sheetData>
